--- a/tests/fixtures/policies_seed7.xlsx
+++ b/tests/fixtures/policies_seed7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cms89\AppData\Roaming\Claude\scratch-workspaces\a72c5ced-5896-445f-ba4c-143e77ffe85d\78e220c2-1d03-4db7-9c30-facaa620e845\scratch-2026-10-19-6e9fe4\v3\tests\fixtures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{171F2813-F130-44C8-A796-0BADB76E7F2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8573562F-D06C-4B81-85E4-791A5D9D9E26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -135,7 +135,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="292">
   <si>
     <t>Aggregate Anxiety: Aggregate Planning in Excel</t>
   </si>
@@ -260,10 +260,10 @@
     <t>Workforce: fractional workers allowed</t>
   </si>
   <si>
-    <t>• Your company can staff in fractions of a worker (part-time hours, shared staff): think of the Workers column as worker-equivalents.</t>
-  </si>
-  <si>
-    <t>• Employ exactly the workforce production needs — 10.2 workers is fine. Do not round.</t>
+    <t>• Your company can staff in fractions of a worker (part-time hours, shared staff), so capacity can be added or removed in small increments instead of a whole worker at a time. Think of the Workers column as worker-equivalents.</t>
+  </si>
+  <si>
+    <t>• Employ exactly the workforce production needs — 10.2 workers is fine. Do not round, so no capacity sits idle just because of rounding.</t>
   </si>
   <si>
     <t>• Labor, hiring and layoff costs are paid in proportion: half a worker hired costs half of HireCost.</t>
@@ -431,7 +431,7 @@
     <t>April</t>
   </si>
   <si>
-    <t>Ending-inventory target your policy sets (see below)</t>
+    <t>Ending-inventory target your safety-stock policy sets (see below)</t>
   </si>
   <si>
     <t>EndTarget</t>
@@ -992,13 +992,25 @@
     <t>created_utc</t>
   </si>
   <si>
-    <t>2026-10-19T19:43:13Z</t>
+    <t>2026-10-19T21:19:29Z</t>
   </si>
   <si>
     <t>workbook_id</t>
   </si>
   <si>
-    <t>2a788575f926</t>
+    <t>b222b96b09f1</t>
+  </si>
+  <si>
+    <t>safety_stock_policy</t>
+  </si>
+  <si>
+    <t>maintain</t>
+  </si>
+  <si>
+    <t>worker_policy</t>
+  </si>
+  <si>
+    <t>partial</t>
   </si>
 </sst>
 </file>
@@ -1735,7 +1747,7 @@
       </c>
       <c r="D35" s="37"/>
     </row>
-    <row r="37" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="7" t="s">
         <v>40</v>
       </c>
@@ -1744,7 +1756,7 @@
       </c>
       <c r="D37" s="37"/>
     </row>
-    <row r="38" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C38" s="38" t="s">
         <v>42</v>
       </c>
@@ -2500,7 +2512,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="38" t="s">
         <v>41</v>
       </c>
@@ -6878,7 +6890,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -6958,6 +6970,22 @@
         <v>287</v>
       </c>
     </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>288</v>
+      </c>
+      <c r="B11" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>290</v>
+      </c>
+      <c r="B12" t="s">
+        <v>291</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
